--- a/data/trans_orig/IP07A19-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A19-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>28914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49804</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50807</t>
+          <t>50326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70967</t>
+          <t>72332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40883</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61643</t>
+          <t>60887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97815</t>
+          <t>96648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126740</t>
+          <t>126354</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>82810</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104993</t>
+          <t>106247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91224</t>
+          <t>90051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114826</t>
+          <t>115244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180306</t>
+          <t>179599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214566</t>
+          <t>214106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74551</t>
+          <t>75270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>86507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113930</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25842</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19739</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27414</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27794</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>41123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36828</t>
+          <t>37111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55639</t>
+          <t>56188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73737</t>
+          <t>74219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>24141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85173</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110797</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63538</t>
+          <t>63770</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89369</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154169</t>
+          <t>155151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191702</t>
+          <t>190342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136482</t>
+          <t>137355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>164732</t>
+          <t>166385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,82 +2906,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>152606</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>137586</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>167172</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>40,04%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>48,65%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>304175</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>282951</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>326760</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>42,63%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>152606</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>138574</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>167432</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>40,33%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>304175</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>282896</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>325099</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61473</t>
+          <t>60500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94924</t>
+          <t>97400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116438</t>
+          <t>117505</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>150349</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>55339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>21645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23021</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63913</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85896</t>
+          <t>85878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65884</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88968</t>
+          <t>90097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>137060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168520</t>
+          <t>169633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>77039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100157</t>
+          <t>101100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76069</t>
+          <t>77616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160843</t>
+          <t>161063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194255</t>
+          <t>193446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>22474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>38844</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83685</t>
+          <t>81312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>32912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38973</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>45007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63692</t>
+          <t>63093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27621</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120095</t>
+          <t>120696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149921</t>
+          <t>149292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>104501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134157</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231952</t>
+          <t>233502</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272900</t>
+          <t>273217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111005</t>
+          <t>111892</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140054</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146264</t>
+          <t>147285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237775</t>
+          <t>238457</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278430</t>
+          <t>279346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>106689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>30678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94019</t>
+          <t>93728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120549</t>
+          <t>119441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72368</t>
+          <t>72892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97198</t>
+          <t>97833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172910</t>
+          <t>174304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209400</t>
+          <t>208939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78252</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102829</t>
+          <t>103223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>77498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103095</t>
+          <t>103243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163717</t>
+          <t>164091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198331</t>
+          <t>198451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>31539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41967</t>
+          <t>41530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>63038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78684</t>
+          <t>78813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107708</t>
+          <t>109338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>19136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>26712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>25428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24474</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38592</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53367</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73860</t>
+          <t>75190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33374</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>39886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>48206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69050</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134608</t>
+          <t>135310</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164484</t>
+          <t>165324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>114693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144312</t>
+          <t>144308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>255471</t>
+          <t>256098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300320</t>
+          <t>299026</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146496</t>
+          <t>147470</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125131</t>
+          <t>124475</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>156677</t>
+          <t>154859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248439</t>
+          <t>251404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294022</t>
+          <t>292480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>44990</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67588</t>
+          <t>67441</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54409</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>79626</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106757</t>
+          <t>106447</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141851</t>
+          <t>141391</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
